--- a/base_prov_co/unidroga/rappi_abbott_2026_09_17.xlsx
+++ b/base_prov_co/unidroga/rappi_abbott_2026_09_17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,55 +451,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -526,20 +531,19 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -547,24 +551,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>38</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>501</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-850-gr-7703186030108/p</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -591,20 +600,19 @@
           <t>7703186032157</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -612,24 +620,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>71</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>386</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-850gr-tarrox400gr-ahorr20--7703186032157/p</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -656,20 +669,19 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -677,24 +689,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>40</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>386</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -721,20 +738,19 @@
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -742,24 +758,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>38</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>386</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-vainilla-tarro-x-400-gr-8427030004549/p</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -786,20 +807,19 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -807,24 +827,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>37</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>386</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-fresa-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -851,20 +876,19 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -872,24 +896,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>35</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>501</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-fresa-tarro-x-850-gr-8710428013859/p</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -916,20 +945,19 @@
           <t>8710428013873</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -937,24 +965,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>35</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>548</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-fresa-tarro-x-400-gr-8710428013873/p</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -981,20 +1014,19 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1002,24 +1034,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>41</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>386</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-chocolate-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1046,20 +1083,19 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1067,24 +1103,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>30</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>501</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-polvo-vainilla-tarro-x-400-gr-8427030003153/p</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1111,20 +1152,19 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1132,24 +1172,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
         <v>4</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>40</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>386</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1176,20 +1221,19 @@
           <t>7703186031433</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1197,24 +1241,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>41</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>457</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-clinical-liquido-vainilla-botella-x-220-ml-7703186031433/p</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1241,20 +1290,19 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1262,24 +1310,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>36</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>407</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-liquido-cafe-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1306,20 +1359,19 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1327,24 +1379,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>34</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>153</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-cafe-x-400-gr/p</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1371,20 +1428,19 @@
           <t>8710428011848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1392,24 +1448,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>39</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>386</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-advance-polvo-chocolate-tarro-x-400-gr-8710428011848/p</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1436,20 +1497,19 @@
           <t>8710428017987</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1457,24 +1517,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>31</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>493</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/ensure-plus-hn-liquido-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1501,20 +1566,19 @@
           <t>7703186069917</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1522,24 +1586,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>27</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>71</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pulmocare-liquido-tarro-x-8-onzas-7703186069917/p</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1566,20 +1635,19 @@
           <t>7703186030191</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1587,24 +1655,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>25</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>756</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/nepro-bp-liquido-lata-x-237-ml-7703186030191/p</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1631,20 +1704,19 @@
           <t>7703186030184</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1652,24 +1724,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>25</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>327</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/nepro-ap-liquido-lata-x-237-ml-7703186030184/p</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1696,20 +1773,19 @@
           <t>8710428022790</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1717,24 +1793,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>33</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>153</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/prosure-liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1761,20 +1842,19 @@
           <t>8699548993756</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1782,24 +1862,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>25</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>233</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/abound-orange-caja-x-30-sobres-8699548993756/p</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1826,20 +1911,19 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1847,24 +1931,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>32</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>370</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1891,20 +1980,19 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1912,24 +2000,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>5</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>34</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>370</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-botella-x-237-ml-7703186030283/p</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1956,20 +2049,19 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1977,24 +2069,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>62</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>370</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-850-gr---glucerna-polvo-vainilla-x-400-gr-precio-especial/p</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2021,20 +2118,19 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2042,24 +2138,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>58</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>370</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-botella-x-237-ml-pack-x-6-und/p</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2086,20 +2187,19 @@
           <t>7703186190376</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2107,24 +2207,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>97</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>153</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-vainilla-x-237-ml--6----glucerna-liquido-fresa-x-237-ml--2--oferta-20--descuento/p</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2151,20 +2256,19 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2172,24 +2276,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>5</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>32</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>370</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-fresa-botella-x-237-ml-7703186031525/p</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2216,20 +2325,19 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2237,24 +2345,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>32</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>370</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-tarro-x-400-gr-7703186031594/p</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2281,20 +2394,19 @@
           <t>7703186358035</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2302,24 +2414,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>74</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>153</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-vainilla-x-400-gr-gratis-glucerna-liquido-vainilla-x-237-ml/p</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2346,20 +2463,19 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2367,24 +2483,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>33</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>153</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-polvo-capuchino-x-400-gr/p</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2411,20 +2532,19 @@
           <t>8710428024299</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2432,24 +2552,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>5</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>43</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>153</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/glucerna-liquido-1-6-kcal-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2476,20 +2601,19 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2497,24 +2621,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>29</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>197</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-uva-frasco-x-500-ml-7501033957376/p</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2541,20 +2670,19 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,24 +2690,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>31</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>197</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-fresa-frasco-x-500-ml-7501033961557/p</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2606,20 +2739,19 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2627,24 +2759,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>33</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>197</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-manzana-frasco-x-500-ml-7501033957369/p</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2671,20 +2808,19 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2692,24 +2828,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>30</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>197</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-60-coco-frasco-x-500-ml-7501033961540/p</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2736,20 +2877,19 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2757,24 +2897,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>35</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>197</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-30-cereza-frasco-x-500-ml-7501033959967/p</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2801,20 +2946,19 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2822,24 +2966,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>34</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>197</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-45-fresa-frasco-x-500-ml-7501033957413/p</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2866,20 +3015,19 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2887,24 +3035,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>33</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>197</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pedialyte-zinc-30-coco-frasco-x-500-ml-7501033959974/p</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2931,20 +3084,19 @@
           <t>7501033959950</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2952,24 +3104,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>47</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>143</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-manzana-115206/p</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2996,20 +3153,19 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3017,24 +3173,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>47</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>143</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-30-durazno-115208/p</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3061,20 +3222,19 @@
           <t>7501033962394</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3082,24 +3242,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J41" t="n">
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>47</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>140</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>https://www.larebajavirtual.com/suero-rehidratacion-pedialyte-active-45-guarana-148796/p</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3126,20 +3291,19 @@
           <t>7703186000026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3147,24 +3311,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>86</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>153</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--polvo-vainilla-x-850-gr-gratis-3-pediasure-10--liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3191,20 +3360,19 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3212,24 +3380,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>5</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>33</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>350</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3256,20 +3429,19 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3277,24 +3449,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
         <v>5</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>34</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>348</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-tarro-x-1600-gr/p</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3321,20 +3498,19 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3342,24 +3518,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>35</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>348</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3386,20 +3567,19 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3407,24 +3587,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
         <v>4</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>32</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>348</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-fresa-botella-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3451,20 +3636,19 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3472,24 +3656,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>5</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>39</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>153</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-fresa-x-850-gr/p</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3516,20 +3705,19 @@
           <t>8710428021885</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3537,24 +3725,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>37</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>153</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--polvo-vainilla-x-850-gr/p</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3581,20 +3774,19 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3602,24 +3794,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>30</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>348</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-fresa-tarro-x-400-gr-7703186027580/p</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3646,20 +3843,19 @@
           <t>7703186799036</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3667,24 +3863,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
         <v>2</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>76</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>153</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-polvo-vainilla-x-400-gr-gratis-pediasure-liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3711,20 +3912,19 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3732,24 +3932,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
         <v>5</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>64</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>348</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-botella-x-220-ml-pack-x-6-und/p</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3776,20 +3981,19 @@
           <t>7703186123480</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3797,24 +4001,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
         <v>2</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>64</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>153</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-liquido-vainilla-x-220-ml-x-8-und-oferta-20--descuento/p</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3841,20 +4050,19 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3862,24 +4070,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
         <v>1</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>39</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>153</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/pediasure-10--liquido-vainilla-x-220-ml/p</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3906,20 +4119,19 @@
           <t>5099864016987</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3927,24 +4139,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>35</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>158</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3971,20 +4188,19 @@
           <t>5099864016994</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3992,24 +4208,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>35</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>358</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4036,20 +4257,19 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4057,24 +4277,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>36</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>175</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-1-caja-x-1400-gr-7703186031860/p</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4101,20 +4326,19 @@
           <t>7703186497345</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4122,24 +4346,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>59</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>168</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-liquido-x-8-botellas-x-59-ml-c-u/p</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4166,20 +4395,19 @@
           <t>5099864017021</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4187,24 +4415,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>36</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>266</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-1800-gr/p</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4231,20 +4464,19 @@
           <t>5099864017014</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4252,24 +4484,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>35</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>479</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4296,20 +4533,19 @@
           <t>5099864017007</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4317,24 +4553,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>35</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>588</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-2-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4361,20 +4602,19 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4382,24 +4622,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
         <v>5</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>35</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>397</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-1800-gr/p</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4426,20 +4671,19 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4447,24 +4691,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>5</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>34</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>606</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-800-gr/p</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4491,20 +4740,19 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4512,24 +4760,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
         <v>5</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>34</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>644</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-3-tarro-x-350-gr/p</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4556,20 +4809,19 @@
           <t>8427030005003</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4577,24 +4829,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
       <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>36</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>774</v>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-ar-tarro--x-850-gr-8427030005003/p</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4621,20 +4878,19 @@
           <t>8427030004938</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4642,24 +4898,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
         <v>1</v>
       </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>36</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>158</v>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-ar-tarro--x-375-gr-8427030004938/p</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4686,20 +4947,19 @@
           <t>7703186029508</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4707,24 +4967,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
         <v>1</v>
       </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
       <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>21</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>171</v>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-mama-tarro-x-400-gr-7703186029508/p</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4751,20 +5016,19 @@
           <t>7703186032836</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4772,24 +5036,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
         <v>1</v>
       </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>48</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>438</v>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-mama-tarro-x-400-gr--2--20--descuento-7703186032836/p</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4816,20 +5085,19 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4837,24 +5105,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J68" t="n">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
       <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>41</v>
       </c>
-      <c r="M68" t="n">
+      <c r="N68" t="n">
         <v>199</v>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-neosure-tarro--x-370-gr-8427030003658/p</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4881,20 +5154,19 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4902,24 +5174,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J69" t="n">
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
         <v>49</v>
       </c>
-      <c r="M69" t="n">
+      <c r="N69" t="n">
         <v>437</v>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-rice-0-12-meses-tarro-x-400-gr/p</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4946,20 +5223,19 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4967,24 +5243,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J70" t="n">
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>45</v>
       </c>
-      <c r="M70" t="n">
+      <c r="N70" t="n">
         <v>318</v>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-sin-lactosa-tarro--x-375-gr-8427030003238/p</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5011,20 +5292,19 @@
           <t>8427030008820</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5032,24 +5312,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J71" t="n">
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
         <v>1</v>
       </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>53</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>286</v>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-2-total-comfort-kid-lata-x-820-gr/p</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5076,20 +5361,19 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5097,24 +5381,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J72" t="n">
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>50</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>376</v>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/similac-total-comfort-1-caja-x-1400-gr-7703186032355/p</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5141,20 +5430,19 @@
           <t>8427030009285</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5162,24 +5450,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J73" t="n">
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
         <v>1</v>
       </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>49</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>153</v>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-total-comfort-x-800-gr/p</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5206,20 +5499,19 @@
           <t>8427030009278</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5227,24 +5519,29 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
       <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>49</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>153</v>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>https://www.tudrogueriavirtual.com/formula-infantil-similac-1-total-comfort-x-350-gr/p</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
